--- a/Verifica_Torino_2027.xlsx
+++ b/Verifica_Torino_2027.xlsx
@@ -8026,52 +8026,37 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="inlineStr">
-        <is>
-          <t>Cru</t>
-        </is>
-      </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>Piazza Emanuele Filiberto, 2/D</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>011/6502183</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr"/>
-      <c r="E132" s="1" t="inlineStr"/>
-      <c r="F132" s="1" t="inlineStr">
-        <is>
-          <t>cru.torino</t>
-        </is>
-      </c>
-      <c r="G132" s="1" t="inlineStr"/>
-      <c r="H132" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I132" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J132" s="1" t="inlineStr"/>
-      <c r="K132" s="1" t="inlineStr"/>
-      <c r="L132" s="1" t="inlineStr"/>
-      <c r="M132" s="1" t="inlineStr"/>
-      <c r="N132" s="1" t="inlineStr"/>
-      <c r="O132" s="1" t="inlineStr"/>
-      <c r="P132" s="1" t="inlineStr"/>
-      <c r="Q132" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: non trovato (cru.torino)</t>
-        </is>
-      </c>
-      <c r="R132" s="1" t="inlineStr">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>La petite cave</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Corso Alcide De Gasperi, 2/b</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>011/595208</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
@@ -8080,17 +8065,32 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>La petite cave</t>
+          <t>Orma vini</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Corso Alcide De Gasperi, 2/b</t>
+          <t>Via Sant'Ottavio, 52/D</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>011/595208</t>
+          <t>011/0567367</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>www.ormabistrot.it</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>OrmaVini</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8103,9 +8103,19 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '18:30', 'closes': '01'}, 'martedì': {'opens': '18:30', 'cl</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (OrmaVini) | IG: nessun handle</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -8117,27 +8127,32 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Orma vini</t>
+          <t>Paltò</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Via Sant'Ottavio, 52/D</t>
+          <t>Via della Rocca, 17</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>011/0567367</t>
+          <t>351/6229996</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>www.ormabistrot.it</t>
+          <t>www.paltotorino.it</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>OrmaVini</t>
+          <t>paltocaffevini</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>palto.torino</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -8145,6 +8160,11 @@
           <t>N/D</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I134" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -8157,7 +8177,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '18:30', 'closes': '01'}, 'martedì': {'opens': '18:30', 'cl</t>
+          <t>{'lunedì': {'opens': '18', 'closes': '00'}, 'martedì': {'opens': '18', 'closes':</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -8167,7 +8187,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (OrmaVini) | IG: nessun handle</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (paltocaffevini) | IG: non trovato (palto.torino)</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -8179,37 +8199,27 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Paltò</t>
+          <t>Piattini - Caffè e Vini</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Via della Rocca, 17</t>
+          <t>Via Corte d'Appello, 9/A</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>351/6229996</t>
+          <t>331/3843390</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>www.paltotorino.it</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>paltocaffevini</t>
+          <t>piattini.eatbu.com</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>palto.torino</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>piattinicaffevini</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8229,7 +8239,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '18', 'closes': '00'}, 'martedì': {'opens': '18', 'closes':</t>
+          <t>{'lunedì': {'opens': '18', 'closes': '23'}, 'martedì': {'opens': '09:30, 18', 'c</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -8239,7 +8249,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (paltocaffevini) | IG: non trovato (palto.torino)</t>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (piattinicaffevini)</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -8251,27 +8261,37 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Piattini - Caffè e Vini</t>
+          <t>Rossorubino</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Via Corte d'Appello, 9/A</t>
+          <t>Via Monferrato, 14</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>331/3843390</t>
+          <t>011/6502183</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>piattini.eatbu.com</t>
+          <t>www.rossorubino.net</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>rossorubino.enoteca</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>piattinicaffevini</t>
+          <t>rossorubino.enoteca</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8291,7 +8311,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '18', 'closes': '23'}, 'martedì': {'opens': '09:30, 18', 'c</t>
+          <t>{'lunedì': {'opens': '10', 'closes': '21'}, 'martedì': {'opens': '10', 'closes':</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -8301,7 +8321,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (piattinicaffevini)</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (rossorubino.enoteca) | IG: trovato (rossorubino.enoteca)</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -8313,42 +8333,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Rossorubino</t>
+          <t>Sodo</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Via Monferrato, 14</t>
+          <t>Via Giambattista Bodoni, 5</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>011/6502183</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>www.rossorubino.net</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>rossorubino.enoteca</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>rossorubino.enoteca</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>392/1257116</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8363,17 +8358,12 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '10', 'closes': '21'}, 'martedì': {'opens': '10', 'closes':</t>
-        </is>
-      </c>
-      <c r="O137" t="inlineStr">
-        <is>
-          <t>Si</t>
+          <t>{'lunedì': {'opens': '18', 'closes': '22'}, 'martedì': {'opens': '18', 'closes':</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (rossorubino.enoteca) | IG: trovato (rossorubino.enoteca)</t>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -8385,17 +8375,42 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Sodo</t>
+          <t>Tastuma</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Via Giambattista Bodoni, 5</t>
+          <t>Via della Consolata, 12</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>392/1257116</t>
+          <t>011/19887600</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>www.tastuma.it</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Tastumacheeseandwinebar</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>tastumatorino</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8410,12 +8425,17 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '18', 'closes': '22'}, 'martedì': {'opens': '18', 'closes':</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '18', 'closes': '00'}, 'mer</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (Tastumacheeseandwinebar) | IG: trovato (tastumatorino)</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -8427,42 +8447,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Tastuma</t>
+          <t>Tut Vin</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Via della Consolata, 12</t>
+          <t>Via Borgo Dora, 12/B</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>011/19887600</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>www.tastuma.it</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Tastumacheeseandwinebar</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>tastumatorino</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>347/4478959</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8475,19 +8470,9 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '18', 'closes': '00'}, 'mer</t>
-        </is>
-      </c>
-      <c r="O139" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (Tastumacheeseandwinebar) | IG: trovato (tastumatorino)</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -8499,17 +8484,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Tut Vin</t>
+          <t>51 Manifattura Alimentare</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Via Borgo Dora, 12/B</t>
+          <t>Lungo Dora Firenze, 51/A</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>347/4478959</t>
+          <t>011/237359</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8522,9 +8507,14 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '10', 'closes': '15'}, 'martedì': {'opens': '10, 18:30', 'c</t>
+        </is>
+      </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -8536,17 +8526,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>51 Manifattura Alimentare</t>
+          <t>Adelaide!</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Lungo Dora Firenze, 51/A</t>
+          <t>Via Giuseppe Mazzini, 58</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>011/237359</t>
+          <t>011/3358459</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8561,12 +8551,12 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '10', 'closes': '15'}, 'martedì': {'opens': '10, 18:30', 'c</t>
+          <t>{'lunedì': {'opens': '07', 'closes': '00'}, 'martedì': {'opens': '07', 'closes':</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -8578,17 +8568,27 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Adelaide!</t>
+          <t>CouCou</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Via Giuseppe Mazzini, 58</t>
+          <t>Via Carlo Ignazio Giulio, 2/G</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>011/3358459</t>
+          <t>011/18837059</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>coucoutorino</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8603,12 +8603,17 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '07', 'closes': '00'}, 'martedì': {'opens': '07', 'closes':</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '18:30', 'closes': '00'}, '</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (coucoutorino)</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -8620,27 +8625,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CouCou</t>
+          <t>Magazzini Oz</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Via Carlo Ignazio Giulio, 2/G</t>
+          <t>Via Giovanni Giolitti, 19/A</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>011/18837059</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>coucoutorino</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>011/0812816</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8655,17 +8650,12 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '18:30', 'closes': '00'}, '</t>
-        </is>
-      </c>
-      <c r="O143" t="inlineStr">
-        <is>
-          <t>Si</t>
+          <t>{'lunedì': {'opens': '08:30', 'closes': '15'}, 'martedì': {'opens': '08:30', 'cl</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (coucoutorino)</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -8677,17 +8667,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Magazzini Oz</t>
+          <t>Muro - osteria contemporanea</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Via Giovanni Giolitti, 19/A</t>
+          <t>Via Cigna, 114/E</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>011/0812816</t>
+          <t>375/7700654</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -8702,12 +8692,12 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '08:30', 'closes': '15'}, 'martedì': {'opens': '08:30', 'cl</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12', 'closes': '15'}, 'mer</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -8719,17 +8709,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Muro - osteria contemporanea</t>
+          <t>Rabarè</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Via Cigna, 114/E</t>
+          <t>Via Maria Vittoria, 58/H</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>375/7700654</t>
+          <t>366/1443776</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -8744,12 +8734,12 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12', 'closes': '15'}, 'mer</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '19', 'closes': '00'}, 'mer</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -8761,17 +8751,42 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Rabarè</t>
+          <t>Recina - focaccia e cucina</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Via Maria Vittoria, 58/H</t>
+          <t>Via della Misericordia, 4/F</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>366/1443776</t>
+          <t>011/6997385</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>www.gaudenziovinoecucina.it/recina</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>recinafocacciaecucina</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>recina-focaccia-e-cucina</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -8784,14 +8799,14 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '19', 'closes': '00'}, 'mer</t>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (recinafocacciaecucina) | IG: trovato (recina-focaccia-e-cucina)</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -8803,42 +8818,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Recina - focaccia e cucina</t>
+          <t>Sciarada</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Via della Misericordia, 4/F</t>
+          <t>Via Claudio Luigi Berthollet, 20/D</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>011/6997385</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>www.gaudenziovinoecucina.it/recina</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>recinafocacciaecucina</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>recina-focaccia-e-cucina</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>340/9599722</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -8851,14 +8841,14 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="O147" t="inlineStr">
-        <is>
-          <t>Si</t>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': 'Chiuso'}, 'mercoledì': {'o</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (recinafocacciaecucina) | IG: trovato (recina-focaccia-e-cucina)</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -8870,17 +8860,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Sciarada</t>
+          <t>Bar Cavour</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Via Claudio Luigi Berthollet, 20/D</t>
+          <t>Piazza Carignano, 2</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>340/9599722</t>
+          <t>011/19211270</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -8893,14 +8883,9 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': 'Chiuso'}, 'mercoledì': {'o</t>
-        </is>
-      </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -8912,17 +8897,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Bar Cavour</t>
+          <t>Barz8</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Piazza Carignano, 2</t>
+          <t>Corso Moncalieri, 5/A</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>011/19211270</t>
+          <t>349/3175425</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -8937,7 +8922,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -8949,17 +8934,27 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Barz8</t>
+          <t>Cru</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Corso Moncalieri, 5/A</t>
+          <t>Piazza Emanuele Filiberto, 2/D</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>349/3175425</t>
+          <t>011/6502183</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>cru.torino</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -8972,74 +8967,81 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>TF: non trovato | FB: nessun handle | IG: trovato (cru.torino)</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="inlineStr">
+      <c r="A151" t="inlineStr">
         <is>
           <t>D.One</t>
         </is>
       </c>
-      <c r="B151" s="1" t="inlineStr">
+      <c r="B151" t="inlineStr">
         <is>
           <t>Via Baretti, 15</t>
         </is>
       </c>
-      <c r="C151" s="1" t="inlineStr">
+      <c r="C151" t="inlineStr">
         <is>
           <t>349/6733755</t>
         </is>
       </c>
-      <c r="D151" s="1" t="inlineStr"/>
-      <c r="E151" s="1" t="inlineStr">
+      <c r="E151" t="inlineStr">
         <is>
           <t>donetorino</t>
         </is>
       </c>
-      <c r="F151" s="1" t="inlineStr">
+      <c r="F151" t="inlineStr">
         <is>
           <t>donetorino</t>
         </is>
       </c>
-      <c r="G151" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H151" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I151" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J151" s="1" t="inlineStr"/>
-      <c r="K151" s="1" t="inlineStr"/>
-      <c r="L151" s="1" t="inlineStr"/>
-      <c r="M151" s="1" t="inlineStr"/>
-      <c r="N151" s="1" t="inlineStr"/>
-      <c r="O151" s="1" t="inlineStr"/>
-      <c r="P151" s="1" t="inlineStr"/>
-      <c r="Q151" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R151" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (donetorino) | IG: trovato (donetorino)</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -9069,7 +9071,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J152" s="1" t="inlineStr"/>
+      <c r="J152" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K152" s="1" t="inlineStr"/>
       <c r="L152" s="1" t="inlineStr"/>
       <c r="M152" s="1" t="inlineStr"/>
@@ -9078,76 +9084,79 @@
       <c r="P152" s="1" t="inlineStr"/>
       <c r="Q152" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="inlineStr">
+      <c r="A153" t="inlineStr">
         <is>
           <t>Smile Tree</t>
         </is>
       </c>
-      <c r="B153" s="1" t="inlineStr">
+      <c r="B153" t="inlineStr">
         <is>
           <t>Piazza della Consolata, 9</t>
         </is>
       </c>
-      <c r="C153" s="1" t="inlineStr">
+      <c r="C153" t="inlineStr">
         <is>
           <t>331/1848136</t>
         </is>
       </c>
-      <c r="D153" s="1" t="inlineStr">
+      <c r="D153" t="inlineStr">
         <is>
           <t>www.smiletreetorino.com</t>
         </is>
       </c>
-      <c r="E153" s="1" t="inlineStr">
+      <c r="E153" t="inlineStr">
         <is>
           <t>SmileTreeTorino</t>
         </is>
       </c>
-      <c r="F153" s="1" t="inlineStr">
+      <c r="F153" t="inlineStr">
         <is>
           <t>smile_tree_torino</t>
         </is>
       </c>
-      <c r="G153" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H153" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I153" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J153" s="1" t="inlineStr"/>
-      <c r="K153" s="1" t="inlineStr"/>
-      <c r="L153" s="1" t="inlineStr"/>
-      <c r="M153" s="1" t="inlineStr"/>
-      <c r="N153" s="1" t="inlineStr"/>
-      <c r="O153" s="1" t="inlineStr"/>
-      <c r="P153" s="1" t="inlineStr"/>
-      <c r="Q153" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R153" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (SmileTreeTorino) | IG: trovato (smile_tree_torino)</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -9177,7 +9186,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J154" s="1" t="inlineStr"/>
+      <c r="J154" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K154" s="1" t="inlineStr"/>
       <c r="L154" s="1" t="inlineStr"/>
       <c r="M154" s="1" t="inlineStr"/>
@@ -9186,72 +9199,74 @@
       <c r="P154" s="1" t="inlineStr"/>
       <c r="Q154" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R154" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="inlineStr">
+      <c r="A155" t="inlineStr">
         <is>
           <t>Aria</t>
         </is>
       </c>
-      <c r="B155" s="1" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>Via Santa Giulia, 32/F</t>
         </is>
       </c>
-      <c r="C155" s="1" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>011/19039749</t>
         </is>
       </c>
-      <c r="D155" s="1" t="inlineStr"/>
-      <c r="E155" s="1" t="inlineStr">
+      <c r="E155" t="inlineStr">
         <is>
           <t>ariagelateria</t>
         </is>
       </c>
-      <c r="F155" s="1" t="inlineStr">
+      <c r="F155" t="inlineStr">
         <is>
           <t>aria_gelateria</t>
         </is>
       </c>
-      <c r="G155" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H155" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I155" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J155" s="1" t="inlineStr"/>
-      <c r="K155" s="1" t="inlineStr"/>
-      <c r="L155" s="1" t="inlineStr"/>
-      <c r="M155" s="1" t="inlineStr"/>
-      <c r="N155" s="1" t="inlineStr"/>
-      <c r="O155" s="1" t="inlineStr"/>
-      <c r="P155" s="1" t="inlineStr"/>
-      <c r="Q155" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R155" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (ariagelateria) | IG: trovato (aria_gelateria)</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -9281,7 +9296,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J156" s="1" t="inlineStr"/>
+      <c r="J156" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K156" s="1" t="inlineStr"/>
       <c r="L156" s="1" t="inlineStr"/>
       <c r="M156" s="1" t="inlineStr"/>
@@ -9290,12 +9309,12 @@
       <c r="P156" s="1" t="inlineStr"/>
       <c r="Q156" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R156" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -9325,7 +9344,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J157" s="1" t="inlineStr"/>
+      <c r="J157" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K157" s="1" t="inlineStr"/>
       <c r="L157" s="1" t="inlineStr"/>
       <c r="M157" s="1" t="inlineStr"/>
@@ -9334,76 +9357,79 @@
       <c r="P157" s="1" t="inlineStr"/>
       <c r="Q157" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="inlineStr">
+      <c r="A158" t="inlineStr">
         <is>
           <t>Conogelato</t>
         </is>
       </c>
-      <c r="B158" s="1" t="inlineStr">
+      <c r="B158" t="inlineStr">
         <is>
           <t>Via Giuseppe Mazzini, 22</t>
         </is>
       </c>
-      <c r="C158" s="1" t="inlineStr">
+      <c r="C158" t="inlineStr">
         <is>
           <t>011/884747</t>
         </is>
       </c>
-      <c r="D158" s="1" t="inlineStr">
+      <c r="D158" t="inlineStr">
         <is>
           <t>www.conogelato.com</t>
         </is>
       </c>
-      <c r="E158" s="1" t="inlineStr">
+      <c r="E158" t="inlineStr">
         <is>
           <t>CONOGELATO</t>
         </is>
       </c>
-      <c r="F158" s="1" t="inlineStr">
+      <c r="F158" t="inlineStr">
         <is>
           <t>_conogelato_</t>
         </is>
       </c>
-      <c r="G158" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H158" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I158" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J158" s="1" t="inlineStr"/>
-      <c r="K158" s="1" t="inlineStr"/>
-      <c r="L158" s="1" t="inlineStr"/>
-      <c r="M158" s="1" t="inlineStr"/>
-      <c r="N158" s="1" t="inlineStr"/>
-      <c r="O158" s="1" t="inlineStr"/>
-      <c r="P158" s="1" t="inlineStr"/>
-      <c r="Q158" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R158" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (CONOGELATO) | IG: trovato (_conogelato_)</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -9433,7 +9459,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J159" s="1" t="inlineStr"/>
+      <c r="J159" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K159" s="1" t="inlineStr"/>
       <c r="L159" s="1" t="inlineStr"/>
       <c r="M159" s="1" t="inlineStr"/>
@@ -9442,76 +9472,79 @@
       <c r="P159" s="1" t="inlineStr"/>
       <c r="Q159" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R159" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="inlineStr">
+      <c r="A160" t="inlineStr">
         <is>
           <t>Gasprin dal 1929</t>
         </is>
       </c>
-      <c r="B160" s="1" t="inlineStr">
+      <c r="B160" t="inlineStr">
         <is>
           <t>Corso San Maurizio, 49/A</t>
         </is>
       </c>
-      <c r="C160" s="1" t="inlineStr">
+      <c r="C160" t="inlineStr">
         <is>
           <t>011/7633587</t>
         </is>
       </c>
-      <c r="D160" s="1" t="inlineStr">
+      <c r="D160" t="inlineStr">
         <is>
           <t>www.gasprin.it</t>
         </is>
       </c>
-      <c r="E160" s="1" t="inlineStr">
+      <c r="E160" t="inlineStr">
         <is>
           <t>Gasprin-dal-1929</t>
         </is>
       </c>
-      <c r="F160" s="1" t="inlineStr">
+      <c r="F160" t="inlineStr">
         <is>
           <t>gaspringelatoedelizie</t>
         </is>
       </c>
-      <c r="G160" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H160" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I160" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J160" s="1" t="inlineStr"/>
-      <c r="K160" s="1" t="inlineStr"/>
-      <c r="L160" s="1" t="inlineStr"/>
-      <c r="M160" s="1" t="inlineStr"/>
-      <c r="N160" s="1" t="inlineStr"/>
-      <c r="O160" s="1" t="inlineStr"/>
-      <c r="P160" s="1" t="inlineStr"/>
-      <c r="Q160" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R160" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (Gasprin-dal-1929) | IG: trovato (gaspringelatoedelizie)</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -9541,7 +9574,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J161" s="1" t="inlineStr"/>
+      <c r="J161" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K161" s="1" t="inlineStr"/>
       <c r="L161" s="1" t="inlineStr"/>
       <c r="M161" s="1" t="inlineStr"/>
@@ -9550,12 +9587,12 @@
       <c r="P161" s="1" t="inlineStr"/>
       <c r="Q161" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R161" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -9585,7 +9622,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J162" s="1" t="inlineStr"/>
+      <c r="J162" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K162" s="1" t="inlineStr"/>
       <c r="L162" s="1" t="inlineStr"/>
       <c r="M162" s="1" t="inlineStr"/>
@@ -9594,12 +9635,12 @@
       <c r="P162" s="1" t="inlineStr"/>
       <c r="Q162" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R162" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -9629,7 +9670,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J163" s="1" t="inlineStr"/>
+      <c r="J163" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K163" s="1" t="inlineStr"/>
       <c r="L163" s="1" t="inlineStr"/>
       <c r="M163" s="1" t="inlineStr"/>
@@ -9638,76 +9683,79 @@
       <c r="P163" s="1" t="inlineStr"/>
       <c r="Q163" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R163" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="inlineStr">
+      <c r="A164" t="inlineStr">
         <is>
           <t>Gofreria Piemonteisa</t>
         </is>
       </c>
-      <c r="B164" s="1" t="inlineStr">
+      <c r="B164" t="inlineStr">
         <is>
           <t>Via San Tommaso, 7</t>
         </is>
       </c>
-      <c r="C164" s="1" t="inlineStr">
+      <c r="C164" t="inlineStr">
         <is>
           <t>349/3926090</t>
         </is>
       </c>
-      <c r="D164" s="1" t="inlineStr">
+      <c r="D164" t="inlineStr">
         <is>
           <t>www.gofreriapiemonteisa.it</t>
         </is>
       </c>
-      <c r="E164" s="1" t="inlineStr">
+      <c r="E164" t="inlineStr">
         <is>
           <t>gofreriapiemontese</t>
         </is>
       </c>
-      <c r="F164" s="1" t="inlineStr">
+      <c r="F164" t="inlineStr">
         <is>
           <t>gofreriapiemonteisa</t>
         </is>
       </c>
-      <c r="G164" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H164" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I164" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J164" s="1" t="inlineStr"/>
-      <c r="K164" s="1" t="inlineStr"/>
-      <c r="L164" s="1" t="inlineStr"/>
-      <c r="M164" s="1" t="inlineStr"/>
-      <c r="N164" s="1" t="inlineStr"/>
-      <c r="O164" s="1" t="inlineStr"/>
-      <c r="P164" s="1" t="inlineStr"/>
-      <c r="Q164" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R164" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (gofreriapiemontese) | IG: trovato (gofreriapiemonteisa)</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -9737,7 +9785,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J165" s="1" t="inlineStr"/>
+      <c r="J165" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K165" s="1" t="inlineStr"/>
       <c r="L165" s="1" t="inlineStr"/>
       <c r="M165" s="1" t="inlineStr"/>
@@ -9746,256 +9798,265 @@
       <c r="P165" s="1" t="inlineStr"/>
       <c r="Q165" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R165" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="inlineStr">
+      <c r="A166" t="inlineStr">
         <is>
           <t>L'Essenza del Gelato</t>
         </is>
       </c>
-      <c r="B166" s="1" t="inlineStr">
+      <c r="B166" t="inlineStr">
         <is>
           <t>Via Principe Amedeo, 21/F</t>
         </is>
       </c>
-      <c r="C166" s="1" t="inlineStr">
+      <c r="C166" t="inlineStr">
         <is>
           <t>011/0767531</t>
         </is>
       </c>
-      <c r="D166" s="1" t="inlineStr"/>
-      <c r="E166" s="1" t="inlineStr">
+      <c r="E166" t="inlineStr">
         <is>
           <t>Essenza.del.Gelato</t>
         </is>
       </c>
-      <c r="F166" s="1" t="inlineStr"/>
-      <c r="G166" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H166" s="1" t="inlineStr"/>
-      <c r="I166" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J166" s="1" t="inlineStr"/>
-      <c r="K166" s="1" t="inlineStr"/>
-      <c r="L166" s="1" t="inlineStr"/>
-      <c r="M166" s="1" t="inlineStr"/>
-      <c r="N166" s="1" t="inlineStr"/>
-      <c r="O166" s="1" t="inlineStr"/>
-      <c r="P166" s="1" t="inlineStr"/>
-      <c r="Q166" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R166" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (Essenza.del.Gelato) | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="inlineStr">
+      <c r="A167" t="inlineStr">
         <is>
           <t>M**Bun</t>
         </is>
       </c>
-      <c r="B167" s="1" t="inlineStr">
+      <c r="B167" t="inlineStr">
         <is>
           <t>Corso Galileo Ferraris, 290</t>
         </is>
       </c>
-      <c r="C167" s="1" t="inlineStr">
+      <c r="C167" t="inlineStr">
         <is>
           <t>011/2425070</t>
         </is>
       </c>
-      <c r="D167" s="1" t="inlineStr">
+      <c r="D167" t="inlineStr">
         <is>
           <t>www.mbun.it</t>
         </is>
       </c>
-      <c r="E167" s="1" t="inlineStr">
+      <c r="E167" t="inlineStr">
         <is>
           <t>mbun.it</t>
         </is>
       </c>
-      <c r="F167" s="1" t="inlineStr">
+      <c r="F167" t="inlineStr">
         <is>
           <t>macbun_official</t>
         </is>
       </c>
-      <c r="G167" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H167" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I167" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J167" s="1" t="inlineStr"/>
-      <c r="K167" s="1" t="inlineStr"/>
-      <c r="L167" s="1" t="inlineStr"/>
-      <c r="M167" s="1" t="inlineStr"/>
-      <c r="N167" s="1" t="inlineStr"/>
-      <c r="O167" s="1" t="inlineStr"/>
-      <c r="P167" s="1" t="inlineStr"/>
-      <c r="Q167" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R167" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (mbun.it) | IG: trovato (macbun_official)</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="inlineStr">
+      <c r="A168" t="inlineStr">
         <is>
           <t>Mara dei Boschi</t>
         </is>
       </c>
-      <c r="B168" s="1" t="inlineStr">
+      <c r="B168" t="inlineStr">
         <is>
           <t>Via Claudio Luigi Berthollet, 30</t>
         </is>
       </c>
-      <c r="C168" s="1" t="inlineStr">
+      <c r="C168" t="inlineStr">
         <is>
           <t>011/0769557</t>
         </is>
       </c>
-      <c r="D168" s="1" t="inlineStr">
+      <c r="D168" t="inlineStr">
         <is>
           <t>www.maradeiboschi.it</t>
         </is>
       </c>
-      <c r="E168" s="1" t="inlineStr">
+      <c r="E168" t="inlineStr">
         <is>
           <t>MaradeiBoschi</t>
         </is>
       </c>
-      <c r="F168" s="1" t="inlineStr">
+      <c r="F168" t="inlineStr">
         <is>
           <t>maradeiboschi</t>
         </is>
       </c>
-      <c r="G168" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H168" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I168" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J168" s="1" t="inlineStr"/>
-      <c r="K168" s="1" t="inlineStr"/>
-      <c r="L168" s="1" t="inlineStr"/>
-      <c r="M168" s="1" t="inlineStr"/>
-      <c r="N168" s="1" t="inlineStr"/>
-      <c r="O168" s="1" t="inlineStr"/>
-      <c r="P168" s="1" t="inlineStr"/>
-      <c r="Q168" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R168" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (MaradeiBoschi) | IG: trovato (maradeiboschi)</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="inlineStr">
+      <c r="A169" t="inlineStr">
         <is>
           <t>Margherì</t>
         </is>
       </c>
-      <c r="B169" s="1" t="inlineStr">
+      <c r="B169" t="inlineStr">
         <is>
           <t>Via Sant'Ottavio, 51/C</t>
         </is>
       </c>
-      <c r="C169" s="1" t="inlineStr">
+      <c r="C169" t="inlineStr">
         <is>
           <t>011/0268025</t>
         </is>
       </c>
-      <c r="D169" s="1" t="inlineStr">
+      <c r="D169" t="inlineStr">
         <is>
           <t>www.margheripizza.it</t>
         </is>
       </c>
-      <c r="E169" s="1" t="inlineStr">
+      <c r="E169" t="inlineStr">
         <is>
           <t>margheripizzaromana</t>
         </is>
       </c>
-      <c r="F169" s="1" t="inlineStr">
+      <c r="F169" t="inlineStr">
         <is>
           <t>margheripizza</t>
         </is>
       </c>
-      <c r="G169" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H169" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I169" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J169" s="1" t="inlineStr"/>
-      <c r="K169" s="1" t="inlineStr"/>
-      <c r="L169" s="1" t="inlineStr"/>
-      <c r="M169" s="1" t="inlineStr"/>
-      <c r="N169" s="1" t="inlineStr"/>
-      <c r="O169" s="1" t="inlineStr"/>
-      <c r="P169" s="1" t="inlineStr"/>
-      <c r="Q169" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R169" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (margheripizzaromana) | IG: trovato (margheripizza)</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -10025,7 +10086,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J170" s="1" t="inlineStr"/>
+      <c r="J170" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K170" s="1" t="inlineStr"/>
       <c r="L170" s="1" t="inlineStr"/>
       <c r="M170" s="1" t="inlineStr"/>
@@ -10034,264 +10099,275 @@
       <c r="P170" s="1" t="inlineStr"/>
       <c r="Q170" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="inlineStr">
+      <c r="A171" t="inlineStr">
         <is>
           <t>Nivà</t>
         </is>
       </c>
-      <c r="B171" s="1" t="inlineStr">
+      <c r="B171" t="inlineStr">
         <is>
           <t>Piazza Vittorio Veneto, 8</t>
         </is>
       </c>
-      <c r="C171" s="1" t="inlineStr">
+      <c r="C171" t="inlineStr">
         <is>
           <t>011/8125064</t>
         </is>
       </c>
-      <c r="D171" s="1" t="inlineStr">
+      <c r="D171" t="inlineStr">
         <is>
           <t>www.nivagelato.com</t>
         </is>
       </c>
-      <c r="E171" s="1" t="inlineStr">
+      <c r="E171" t="inlineStr">
         <is>
           <t>nivagelato</t>
         </is>
       </c>
-      <c r="F171" s="1" t="inlineStr">
+      <c r="F171" t="inlineStr">
         <is>
           <t>nivagelato</t>
         </is>
       </c>
-      <c r="G171" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H171" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I171" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J171" s="1" t="inlineStr"/>
-      <c r="K171" s="1" t="inlineStr"/>
-      <c r="L171" s="1" t="inlineStr"/>
-      <c r="M171" s="1" t="inlineStr"/>
-      <c r="N171" s="1" t="inlineStr"/>
-      <c r="O171" s="1" t="inlineStr"/>
-      <c r="P171" s="1" t="inlineStr"/>
-      <c r="Q171" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R171" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (nivagelato) | IG: trovato (nivagelato)</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="inlineStr">
+      <c r="A172" t="inlineStr">
         <is>
           <t>Papalele</t>
         </is>
       </c>
-      <c r="B172" s="1" t="inlineStr">
+      <c r="B172" t="inlineStr">
         <is>
           <t>Corso Guglielmo Marconi, 23/A</t>
         </is>
       </c>
-      <c r="C172" s="1" t="inlineStr">
+      <c r="C172" t="inlineStr">
         <is>
           <t>011/9776990</t>
         </is>
       </c>
-      <c r="D172" s="1" t="inlineStr">
+      <c r="D172" t="inlineStr">
         <is>
           <t>www.papalele.it</t>
         </is>
       </c>
-      <c r="E172" s="1" t="inlineStr">
+      <c r="E172" t="inlineStr">
         <is>
           <t>papalele.gelatiepasticci</t>
         </is>
       </c>
-      <c r="F172" s="1" t="inlineStr">
+      <c r="F172" t="inlineStr">
         <is>
           <t>papalele.gelatiepasticci</t>
         </is>
       </c>
-      <c r="G172" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H172" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I172" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J172" s="1" t="inlineStr"/>
-      <c r="K172" s="1" t="inlineStr"/>
-      <c r="L172" s="1" t="inlineStr"/>
-      <c r="M172" s="1" t="inlineStr"/>
-      <c r="N172" s="1" t="inlineStr"/>
-      <c r="O172" s="1" t="inlineStr"/>
-      <c r="P172" s="1" t="inlineStr"/>
-      <c r="Q172" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R172" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (papalele.gelatiepasticci) | IG: trovato (papalele.gelatiepasticci)</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="inlineStr">
+      <c r="A173" t="inlineStr">
         <is>
           <t>Più di un gelato</t>
         </is>
       </c>
-      <c r="B173" s="1" t="inlineStr">
+      <c r="B173" t="inlineStr">
         <is>
           <t>Via Cesare Battisti, 7/F</t>
         </is>
       </c>
-      <c r="C173" s="1" t="inlineStr">
+      <c r="C173" t="inlineStr">
         <is>
           <t>345/1862428</t>
         </is>
       </c>
-      <c r="D173" s="1" t="inlineStr">
+      <c r="D173" t="inlineStr">
         <is>
           <t>www.piudiungelato.it</t>
         </is>
       </c>
-      <c r="E173" s="1" t="inlineStr">
+      <c r="E173" t="inlineStr">
         <is>
           <t>Piudiungelato</t>
         </is>
       </c>
-      <c r="F173" s="1" t="inlineStr">
+      <c r="F173" t="inlineStr">
         <is>
           <t>piudiungelato</t>
         </is>
       </c>
-      <c r="G173" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H173" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I173" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J173" s="1" t="inlineStr"/>
-      <c r="K173" s="1" t="inlineStr"/>
-      <c r="L173" s="1" t="inlineStr"/>
-      <c r="M173" s="1" t="inlineStr"/>
-      <c r="N173" s="1" t="inlineStr"/>
-      <c r="O173" s="1" t="inlineStr"/>
-      <c r="P173" s="1" t="inlineStr"/>
-      <c r="Q173" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R173" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (Piudiungelato) | IG: trovato (piudiungelato)</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="inlineStr">
+      <c r="A174" t="inlineStr">
         <is>
           <t>Roberta - focacceria genovese</t>
         </is>
       </c>
-      <c r="B174" s="1" t="inlineStr">
+      <c r="B174" t="inlineStr">
         <is>
           <t>Via San Tommaso, 8</t>
         </is>
       </c>
-      <c r="C174" s="1" t="inlineStr">
+      <c r="C174" t="inlineStr">
         <is>
           <t>333/5826556</t>
         </is>
       </c>
-      <c r="D174" s="1" t="inlineStr"/>
-      <c r="E174" s="1" t="inlineStr">
+      <c r="E174" t="inlineStr">
         <is>
           <t>focacceriaroberta</t>
         </is>
       </c>
-      <c r="F174" s="1" t="inlineStr">
+      <c r="F174" t="inlineStr">
         <is>
           <t>robertafocacceria</t>
         </is>
       </c>
-      <c r="G174" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H174" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I174" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J174" s="1" t="inlineStr"/>
-      <c r="K174" s="1" t="inlineStr"/>
-      <c r="L174" s="1" t="inlineStr"/>
-      <c r="M174" s="1" t="inlineStr"/>
-      <c r="N174" s="1" t="inlineStr"/>
-      <c r="O174" s="1" t="inlineStr"/>
-      <c r="P174" s="1" t="inlineStr"/>
-      <c r="Q174" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R174" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (focacceriaroberta) | IG: trovato (robertafocacceria)</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -10321,7 +10397,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J175" s="1" t="inlineStr"/>
+      <c r="J175" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K175" s="1" t="inlineStr"/>
       <c r="L175" s="1" t="inlineStr"/>
       <c r="M175" s="1" t="inlineStr"/>
@@ -10330,332 +10410,347 @@
       <c r="P175" s="1" t="inlineStr"/>
       <c r="Q175" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="inlineStr">
+      <c r="A176" t="inlineStr">
         <is>
           <t>Silvano Gelato d'Altri Tempi</t>
         </is>
       </c>
-      <c r="B176" s="1" t="inlineStr">
+      <c r="B176" t="inlineStr">
         <is>
           <t>Via Nizza, 142</t>
         </is>
       </c>
-      <c r="C176" s="1" t="inlineStr">
+      <c r="C176" t="inlineStr">
         <is>
           <t>011/6677262</t>
         </is>
       </c>
-      <c r="D176" s="1" t="inlineStr">
+      <c r="D176" t="inlineStr">
         <is>
           <t>www.gelateriasilvano.it</t>
         </is>
       </c>
-      <c r="E176" s="1" t="inlineStr">
+      <c r="E176" t="inlineStr">
         <is>
           <t>Silvanogelatodaltritempi</t>
         </is>
       </c>
-      <c r="F176" s="1" t="inlineStr">
+      <c r="F176" t="inlineStr">
         <is>
           <t>silvanogelatodaltritempi</t>
         </is>
       </c>
-      <c r="G176" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H176" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I176" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J176" s="1" t="inlineStr"/>
-      <c r="K176" s="1" t="inlineStr"/>
-      <c r="L176" s="1" t="inlineStr"/>
-      <c r="M176" s="1" t="inlineStr"/>
-      <c r="N176" s="1" t="inlineStr"/>
-      <c r="O176" s="1" t="inlineStr"/>
-      <c r="P176" s="1" t="inlineStr"/>
-      <c r="Q176" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R176" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (Silvanogelatodaltritempi) | IG: trovato (silvanogelatodaltritempi)</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="inlineStr">
+      <c r="A177" t="inlineStr">
         <is>
           <t>Taglio - La pizza per fetta</t>
         </is>
       </c>
-      <c r="B177" s="1" t="inlineStr">
+      <c r="B177" t="inlineStr">
         <is>
           <t>Largo IV Marzo, 17/C</t>
         </is>
       </c>
-      <c r="C177" s="1" t="inlineStr">
+      <c r="C177" t="inlineStr">
         <is>
           <t>011/5215575</t>
         </is>
       </c>
-      <c r="D177" s="1" t="inlineStr">
+      <c r="D177" t="inlineStr">
         <is>
           <t>www.taglioperfetta.com</t>
         </is>
       </c>
-      <c r="E177" s="1" t="inlineStr">
+      <c r="E177" t="inlineStr">
         <is>
           <t>taglioperfetta</t>
         </is>
       </c>
-      <c r="F177" s="1" t="inlineStr">
+      <c r="F177" t="inlineStr">
         <is>
           <t>taglioperfetta</t>
         </is>
       </c>
-      <c r="G177" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H177" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I177" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J177" s="1" t="inlineStr"/>
-      <c r="K177" s="1" t="inlineStr"/>
-      <c r="L177" s="1" t="inlineStr"/>
-      <c r="M177" s="1" t="inlineStr"/>
-      <c r="N177" s="1" t="inlineStr"/>
-      <c r="O177" s="1" t="inlineStr"/>
-      <c r="P177" s="1" t="inlineStr"/>
-      <c r="Q177" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R177" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (taglioperfetta) | IG: trovato (taglioperfetta)</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="inlineStr">
+      <c r="A178" t="inlineStr">
         <is>
           <t>Tellia</t>
         </is>
       </c>
-      <c r="B178" s="1" t="inlineStr">
+      <c r="B178" t="inlineStr">
         <is>
           <t>Via Maria Vittoria, 20</t>
         </is>
       </c>
-      <c r="C178" s="1" t="inlineStr">
+      <c r="C178" t="inlineStr">
         <is>
           <t>011/2481776</t>
         </is>
       </c>
-      <c r="D178" s="1" t="inlineStr">
+      <c r="D178" t="inlineStr">
         <is>
           <t>www.tellia.it</t>
         </is>
       </c>
-      <c r="E178" s="1" t="inlineStr">
+      <c r="E178" t="inlineStr">
         <is>
           <t>TelliaTorino</t>
         </is>
       </c>
-      <c r="F178" s="1" t="inlineStr">
+      <c r="F178" t="inlineStr">
         <is>
           <t>telliatorino</t>
         </is>
       </c>
-      <c r="G178" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H178" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I178" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J178" s="1" t="inlineStr"/>
-      <c r="K178" s="1" t="inlineStr"/>
-      <c r="L178" s="1" t="inlineStr"/>
-      <c r="M178" s="1" t="inlineStr"/>
-      <c r="N178" s="1" t="inlineStr"/>
-      <c r="O178" s="1" t="inlineStr"/>
-      <c r="P178" s="1" t="inlineStr"/>
-      <c r="Q178" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R178" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (TelliaTorino) | IG: trovato (telliatorino)</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="inlineStr">
+      <c r="A179" t="inlineStr">
         <is>
           <t>Trapizzino</t>
         </is>
       </c>
-      <c r="B179" s="1" t="inlineStr">
+      <c r="B179" t="inlineStr">
         <is>
           <t>Piazza Carlo Emanuele II, 17</t>
         </is>
       </c>
-      <c r="C179" s="1" t="inlineStr">
+      <c r="C179" t="inlineStr">
         <is>
           <t>011/18755933</t>
         </is>
       </c>
-      <c r="D179" s="1" t="inlineStr">
+      <c r="D179" t="inlineStr">
         <is>
           <t>www.trapizzino.it</t>
         </is>
       </c>
-      <c r="E179" s="1" t="inlineStr">
+      <c r="E179" t="inlineStr">
         <is>
           <t>Trapizzino</t>
         </is>
       </c>
-      <c r="F179" s="1" t="inlineStr">
+      <c r="F179" t="inlineStr">
         <is>
           <t>Trapizzino</t>
         </is>
       </c>
-      <c r="G179" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H179" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I179" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J179" s="1" t="inlineStr"/>
-      <c r="K179" s="1" t="inlineStr"/>
-      <c r="L179" s="1" t="inlineStr"/>
-      <c r="M179" s="1" t="inlineStr"/>
-      <c r="N179" s="1" t="inlineStr"/>
-      <c r="O179" s="1" t="inlineStr"/>
-      <c r="P179" s="1" t="inlineStr"/>
-      <c r="Q179" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R179" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (Trapizzino) | IG: trovato (Trapizzino)</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="inlineStr">
+      <c r="A180" t="inlineStr">
         <is>
           <t>Vanilla - Creams &amp; Fruits</t>
         </is>
       </c>
-      <c r="B180" s="1" t="inlineStr">
+      <c r="B180" t="inlineStr">
         <is>
           <t>Via Palazzo di Città, 7/B</t>
         </is>
       </c>
-      <c r="C180" s="1" t="inlineStr">
+      <c r="C180" t="inlineStr">
         <is>
           <t>011/4362745</t>
         </is>
       </c>
-      <c r="D180" s="1" t="inlineStr">
+      <c r="D180" t="inlineStr">
         <is>
           <t>www.vanillacreams.it</t>
         </is>
       </c>
-      <c r="E180" s="1" t="inlineStr">
+      <c r="E180" t="inlineStr">
         <is>
           <t>VanillaCreamsAndFruits</t>
         </is>
       </c>
-      <c r="F180" s="1" t="inlineStr">
+      <c r="F180" t="inlineStr">
         <is>
           <t>vanillatorino</t>
         </is>
       </c>
-      <c r="G180" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H180" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I180" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J180" s="1" t="inlineStr"/>
-      <c r="K180" s="1" t="inlineStr"/>
-      <c r="L180" s="1" t="inlineStr"/>
-      <c r="M180" s="1" t="inlineStr"/>
-      <c r="N180" s="1" t="inlineStr"/>
-      <c r="O180" s="1" t="inlineStr"/>
-      <c r="P180" s="1" t="inlineStr"/>
-      <c r="Q180" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R180" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (VanillaCreamsAndFruits) | IG: trovato (vanillatorino)</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Torino_2027.xlsx
+++ b/Verifica_Torino_2027.xlsx
@@ -9046,48 +9046,67 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="inlineStr">
-        <is>
-          <t>Lumeria</t>
-        </is>
-      </c>
-      <c r="B152" s="1" t="inlineStr">
-        <is>
-          <t>Via Reggio, 6/c</t>
-        </is>
-      </c>
-      <c r="C152" s="1" t="inlineStr">
-        <is>
-          <t>011/19707614</t>
-        </is>
-      </c>
-      <c r="D152" s="1" t="inlineStr"/>
-      <c r="E152" s="1" t="inlineStr"/>
-      <c r="F152" s="1" t="inlineStr"/>
-      <c r="G152" s="1" t="inlineStr"/>
-      <c r="H152" s="1" t="inlineStr"/>
-      <c r="I152" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J152" s="1" t="inlineStr">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Smile Tree</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Piazza della Consolata, 9</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>331/1848136</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>www.smiletreetorino.com</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>SmileTreeTorino</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>smile_tree_torino</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K152" s="1" t="inlineStr"/>
-      <c r="L152" s="1" t="inlineStr"/>
-      <c r="M152" s="1" t="inlineStr"/>
-      <c r="N152" s="1" t="inlineStr"/>
-      <c r="O152" s="1" t="inlineStr"/>
-      <c r="P152" s="1" t="inlineStr"/>
-      <c r="Q152" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R152" s="1" t="inlineStr">
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (SmileTreeTorino) | IG: trovato (smile_tree_torino)</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
         <is>
           <t>21/05/2026</t>
         </is>
@@ -9096,32 +9115,27 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Smile Tree</t>
+          <t>Aria</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Piazza della Consolata, 9</t>
+          <t>Via Santa Giulia, 32/F</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>331/1848136</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>www.smiletreetorino.com</t>
+          <t>011/19039749</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>SmileTreeTorino</t>
+          <t>ariagelateria</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>smile_tree_torino</t>
+          <t>aria_gelateria</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -9151,7 +9165,7 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (SmileTreeTorino) | IG: trovato (smile_tree_torino)</t>
+          <t>TF: non trovato | FB: trovato (ariagelateria) | IG: trovato (aria_gelateria)</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -9161,48 +9175,67 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="inlineStr">
-        <is>
-          <t>Snodo</t>
-        </is>
-      </c>
-      <c r="B154" s="1" t="inlineStr">
-        <is>
-          <t>Corso Castefidardo, 22</t>
-        </is>
-      </c>
-      <c r="C154" s="1" t="inlineStr">
-        <is>
-          <t>011/0243771</t>
-        </is>
-      </c>
-      <c r="D154" s="1" t="inlineStr"/>
-      <c r="E154" s="1" t="inlineStr"/>
-      <c r="F154" s="1" t="inlineStr"/>
-      <c r="G154" s="1" t="inlineStr"/>
-      <c r="H154" s="1" t="inlineStr"/>
-      <c r="I154" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J154" s="1" t="inlineStr">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Conogelato</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Via Giuseppe Mazzini, 22</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>011/884747</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>www.conogelato.com</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>CONOGELATO</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>_conogelato_</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K154" s="1" t="inlineStr"/>
-      <c r="L154" s="1" t="inlineStr"/>
-      <c r="M154" s="1" t="inlineStr"/>
-      <c r="N154" s="1" t="inlineStr"/>
-      <c r="O154" s="1" t="inlineStr"/>
-      <c r="P154" s="1" t="inlineStr"/>
-      <c r="Q154" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R154" s="1" t="inlineStr">
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (CONOGELATO) | IG: trovato (_conogelato_)</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
         <is>
           <t>21/05/2026</t>
         </is>
@@ -9211,27 +9244,32 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Aria</t>
+          <t>Gasprin dal 1929</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Via Santa Giulia, 32/F</t>
+          <t>Corso San Maurizio, 49/A</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>011/19039749</t>
+          <t>011/7633587</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>www.gasprin.it</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>ariagelateria</t>
+          <t>Gasprin-dal-1929</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>aria_gelateria</t>
+          <t>gaspringelatoedelizie</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -9261,7 +9299,7 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (ariagelateria) | IG: trovato (aria_gelateria)</t>
+          <t>TF: non trovato | FB: trovato (Gasprin-dal-1929) | IG: trovato (gaspringelatoedelizie)</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
@@ -9271,96 +9309,119 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="inlineStr">
-        <is>
-          <t>Casa Clara</t>
-        </is>
-      </c>
-      <c r="B156" s="1" t="inlineStr">
-        <is>
-          <t>Via Stradella, 187/D</t>
-        </is>
-      </c>
-      <c r="C156" s="1" t="inlineStr">
-        <is>
-          <t>351/7516005</t>
-        </is>
-      </c>
-      <c r="D156" s="1" t="inlineStr"/>
-      <c r="E156" s="1" t="inlineStr"/>
-      <c r="F156" s="1" t="inlineStr"/>
-      <c r="G156" s="1" t="inlineStr"/>
-      <c r="H156" s="1" t="inlineStr"/>
-      <c r="I156" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J156" s="1" t="inlineStr">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Gofreria Piemonteisa</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Via San Tommaso, 7</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>349/3926090</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>www.gofreriapiemonteisa.it</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>gofreriapiemontese</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>gofreriapiemonteisa</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K156" s="1" t="inlineStr"/>
-      <c r="L156" s="1" t="inlineStr"/>
-      <c r="M156" s="1" t="inlineStr"/>
-      <c r="N156" s="1" t="inlineStr"/>
-      <c r="O156" s="1" t="inlineStr"/>
-      <c r="P156" s="1" t="inlineStr"/>
-      <c r="Q156" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R156" s="1" t="inlineStr">
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (gofreriapiemontese) | IG: trovato (gofreriapiemonteisa)</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
         <is>
           <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="inlineStr">
-        <is>
-          <t>Ciacci</t>
-        </is>
-      </c>
-      <c r="B157" s="1" t="inlineStr">
-        <is>
-          <t>Corso Belgio, 176</t>
-        </is>
-      </c>
-      <c r="C157" s="1" t="inlineStr">
-        <is>
-          <t>392/0073855</t>
-        </is>
-      </c>
-      <c r="D157" s="1" t="inlineStr"/>
-      <c r="E157" s="1" t="inlineStr"/>
-      <c r="F157" s="1" t="inlineStr"/>
-      <c r="G157" s="1" t="inlineStr"/>
-      <c r="H157" s="1" t="inlineStr"/>
-      <c r="I157" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J157" s="1" t="inlineStr">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>L'Essenza del Gelato</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Via Principe Amedeo, 21/F</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>011/0767531</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Essenza.del.Gelato</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K157" s="1" t="inlineStr"/>
-      <c r="L157" s="1" t="inlineStr"/>
-      <c r="M157" s="1" t="inlineStr"/>
-      <c r="N157" s="1" t="inlineStr"/>
-      <c r="O157" s="1" t="inlineStr"/>
-      <c r="P157" s="1" t="inlineStr"/>
-      <c r="Q157" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R157" s="1" t="inlineStr">
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (Essenza.del.Gelato) | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
         <is>
           <t>21/05/2026</t>
         </is>
@@ -9369,32 +9430,32 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Conogelato</t>
+          <t>M**Bun</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Via Giuseppe Mazzini, 22</t>
+          <t>Corso Galileo Ferraris, 290</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>011/884747</t>
+          <t>011/2425070</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>www.conogelato.com</t>
+          <t>www.mbun.it</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>CONOGELATO</t>
+          <t>mbun.it</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>_conogelato_</t>
+          <t>macbun_official</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -9424,7 +9485,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (CONOGELATO) | IG: trovato (_conogelato_)</t>
+          <t>TF: non trovato | FB: trovato (mbun.it) | IG: trovato (macbun_official)</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -9434,48 +9495,67 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="inlineStr">
-        <is>
-          <t>Dolce Mania dei Fratelli Lepori</t>
-        </is>
-      </c>
-      <c r="B159" s="1" t="inlineStr">
-        <is>
-          <t>Via Guido Reni, 205</t>
-        </is>
-      </c>
-      <c r="C159" s="1" t="inlineStr">
-        <is>
-          <t>329/6543797</t>
-        </is>
-      </c>
-      <c r="D159" s="1" t="inlineStr"/>
-      <c r="E159" s="1" t="inlineStr"/>
-      <c r="F159" s="1" t="inlineStr"/>
-      <c r="G159" s="1" t="inlineStr"/>
-      <c r="H159" s="1" t="inlineStr"/>
-      <c r="I159" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J159" s="1" t="inlineStr">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Mara dei Boschi</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Via Claudio Luigi Berthollet, 30</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>011/0769557</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>www.maradeiboschi.it</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>MaradeiBoschi</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>maradeiboschi</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K159" s="1" t="inlineStr"/>
-      <c r="L159" s="1" t="inlineStr"/>
-      <c r="M159" s="1" t="inlineStr"/>
-      <c r="N159" s="1" t="inlineStr"/>
-      <c r="O159" s="1" t="inlineStr"/>
-      <c r="P159" s="1" t="inlineStr"/>
-      <c r="Q159" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R159" s="1" t="inlineStr">
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (MaradeiBoschi) | IG: trovato (maradeiboschi)</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
         <is>
           <t>21/05/2026</t>
         </is>
@@ -9484,32 +9564,32 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Gasprin dal 1929</t>
+          <t>Margherì</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Corso San Maurizio, 49/A</t>
+          <t>Via Sant'Ottavio, 51/C</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>011/7633587</t>
+          <t>011/0268025</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>www.gasprin.it</t>
+          <t>www.margheripizza.it</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Gasprin-dal-1929</t>
+          <t>margheripizzaromana</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>gaspringelatoedelizie</t>
+          <t>margheripizza</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -9539,7 +9619,7 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (Gasprin-dal-1929) | IG: trovato (gaspringelatoedelizie)</t>
+          <t>TF: non trovato | FB: trovato (margheripizzaromana) | IG: trovato (margheripizza)</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -9549,144 +9629,201 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="inlineStr">
-        <is>
-          <t>Gelateria La Tosca</t>
-        </is>
-      </c>
-      <c r="B161" s="1" t="inlineStr">
-        <is>
-          <t>Via Luigi Cibrario, 50</t>
-        </is>
-      </c>
-      <c r="C161" s="1" t="inlineStr">
-        <is>
-          <t>011/4379807</t>
-        </is>
-      </c>
-      <c r="D161" s="1" t="inlineStr"/>
-      <c r="E161" s="1" t="inlineStr"/>
-      <c r="F161" s="1" t="inlineStr"/>
-      <c r="G161" s="1" t="inlineStr"/>
-      <c r="H161" s="1" t="inlineStr"/>
-      <c r="I161" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J161" s="1" t="inlineStr">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Nivà</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Piazza Vittorio Veneto, 8</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>011/8125064</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>www.nivagelato.com</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>nivagelato</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>nivagelato</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K161" s="1" t="inlineStr"/>
-      <c r="L161" s="1" t="inlineStr"/>
-      <c r="M161" s="1" t="inlineStr"/>
-      <c r="N161" s="1" t="inlineStr"/>
-      <c r="O161" s="1" t="inlineStr"/>
-      <c r="P161" s="1" t="inlineStr"/>
-      <c r="Q161" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R161" s="1" t="inlineStr">
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (nivagelato) | IG: trovato (nivagelato)</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
         <is>
           <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="inlineStr">
-        <is>
-          <t>Gelati D'Antan</t>
-        </is>
-      </c>
-      <c r="B162" s="1" t="inlineStr">
-        <is>
-          <t>Via Nicola Fabrizi, 37/C</t>
-        </is>
-      </c>
-      <c r="C162" s="1" t="inlineStr">
-        <is>
-          <t>331/4675801</t>
-        </is>
-      </c>
-      <c r="D162" s="1" t="inlineStr"/>
-      <c r="E162" s="1" t="inlineStr"/>
-      <c r="F162" s="1" t="inlineStr"/>
-      <c r="G162" s="1" t="inlineStr"/>
-      <c r="H162" s="1" t="inlineStr"/>
-      <c r="I162" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J162" s="1" t="inlineStr">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Papalele</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Corso Guglielmo Marconi, 23/A</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>011/9776990</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>www.papalele.it</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>papalele.gelatiepasticci</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>papalele.gelatiepasticci</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K162" s="1" t="inlineStr"/>
-      <c r="L162" s="1" t="inlineStr"/>
-      <c r="M162" s="1" t="inlineStr"/>
-      <c r="N162" s="1" t="inlineStr"/>
-      <c r="O162" s="1" t="inlineStr"/>
-      <c r="P162" s="1" t="inlineStr"/>
-      <c r="Q162" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R162" s="1" t="inlineStr">
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (papalele.gelatiepasticci) | IG: trovato (papalele.gelatiepasticci)</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
         <is>
           <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="inlineStr">
-        <is>
-          <t>Gelato DOK Dell'Agnese</t>
-        </is>
-      </c>
-      <c r="B163" s="1" t="inlineStr">
-        <is>
-          <t>Corso Unione Sovietica, 415</t>
-        </is>
-      </c>
-      <c r="C163" s="1" t="inlineStr">
-        <is>
-          <t>011/616157</t>
-        </is>
-      </c>
-      <c r="D163" s="1" t="inlineStr"/>
-      <c r="E163" s="1" t="inlineStr"/>
-      <c r="F163" s="1" t="inlineStr"/>
-      <c r="G163" s="1" t="inlineStr"/>
-      <c r="H163" s="1" t="inlineStr"/>
-      <c r="I163" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J163" s="1" t="inlineStr">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Più di un gelato</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Via Cesare Battisti, 7/F</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>345/1862428</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>www.piudiungelato.it</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Piudiungelato</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>piudiungelato</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K163" s="1" t="inlineStr"/>
-      <c r="L163" s="1" t="inlineStr"/>
-      <c r="M163" s="1" t="inlineStr"/>
-      <c r="N163" s="1" t="inlineStr"/>
-      <c r="O163" s="1" t="inlineStr"/>
-      <c r="P163" s="1" t="inlineStr"/>
-      <c r="Q163" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R163" s="1" t="inlineStr">
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (Piudiungelato) | IG: trovato (piudiungelato)</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
         <is>
           <t>21/05/2026</t>
         </is>
@@ -9695,32 +9832,27 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Gofreria Piemonteisa</t>
+          <t>Roberta - focacceria genovese</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Via San Tommaso, 7</t>
+          <t>Via San Tommaso, 8</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>349/3926090</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>www.gofreriapiemonteisa.it</t>
+          <t>333/5826556</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>gofreriapiemontese</t>
+          <t>focacceriaroberta</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>gofreriapiemonteisa</t>
+          <t>robertafocacceria</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -9750,7 +9882,7 @@
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (gofreriapiemontese) | IG: trovato (gofreriapiemonteisa)</t>
+          <t>TF: non trovato | FB: trovato (focacceriaroberta) | IG: trovato (robertafocacceria)</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -9760,48 +9892,67 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="inlineStr">
-        <is>
-          <t>Il Gelato Amico</t>
-        </is>
-      </c>
-      <c r="B165" s="1" t="inlineStr">
-        <is>
-          <t>Via Principi d'Acaja, 47</t>
-        </is>
-      </c>
-      <c r="C165" s="1" t="inlineStr">
-        <is>
-          <t>347/3492737</t>
-        </is>
-      </c>
-      <c r="D165" s="1" t="inlineStr"/>
-      <c r="E165" s="1" t="inlineStr"/>
-      <c r="F165" s="1" t="inlineStr"/>
-      <c r="G165" s="1" t="inlineStr"/>
-      <c r="H165" s="1" t="inlineStr"/>
-      <c r="I165" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J165" s="1" t="inlineStr">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Silvano Gelato d'Altri Tempi</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Via Nizza, 142</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>011/6677262</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>www.gelateriasilvano.it</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Silvanogelatodaltritempi</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>silvanogelatodaltritempi</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K165" s="1" t="inlineStr"/>
-      <c r="L165" s="1" t="inlineStr"/>
-      <c r="M165" s="1" t="inlineStr"/>
-      <c r="N165" s="1" t="inlineStr"/>
-      <c r="O165" s="1" t="inlineStr"/>
-      <c r="P165" s="1" t="inlineStr"/>
-      <c r="Q165" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R165" s="1" t="inlineStr">
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (Silvanogelatodaltritempi) | IG: trovato (silvanogelatodaltritempi)</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
         <is>
           <t>21/05/2026</t>
         </is>
@@ -9810,22 +9961,32 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>L'Essenza del Gelato</t>
+          <t>Taglio - La pizza per fetta</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Via Principe Amedeo, 21/F</t>
+          <t>Largo IV Marzo, 17/C</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>011/0767531</t>
+          <t>011/5215575</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>www.taglioperfetta.com</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Essenza.del.Gelato</t>
+          <t>taglioperfetta</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>taglioperfetta</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -9833,6 +9994,11 @@
           <t>N/D</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I166" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -9850,7 +10016,7 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (Essenza.del.Gelato) | IG: nessun handle</t>
+          <t>TF: non trovato | FB: trovato (taglioperfetta) | IG: trovato (taglioperfetta)</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -9862,32 +10028,32 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>M**Bun</t>
+          <t>Tellia</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Corso Galileo Ferraris, 290</t>
+          <t>Via Maria Vittoria, 20</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>011/2425070</t>
+          <t>011/2481776</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>www.mbun.it</t>
+          <t>www.tellia.it</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>mbun.it</t>
+          <t>TelliaTorino</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>macbun_official</t>
+          <t>telliatorino</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -9917,7 +10083,7 @@
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (mbun.it) | IG: trovato (macbun_official)</t>
+          <t>TF: non trovato | FB: trovato (TelliaTorino) | IG: trovato (telliatorino)</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
@@ -9929,32 +10095,32 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Mara dei Boschi</t>
+          <t>Trapizzino</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Via Claudio Luigi Berthollet, 30</t>
+          <t>Piazza Carlo Emanuele II, 17</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>011/0769557</t>
+          <t>011/18755933</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>www.maradeiboschi.it</t>
+          <t>www.trapizzino.it</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>MaradeiBoschi</t>
+          <t>Trapizzino</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>maradeiboschi</t>
+          <t>Trapizzino</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -9984,7 +10150,7 @@
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (MaradeiBoschi) | IG: trovato (maradeiboschi)</t>
+          <t>TF: non trovato | FB: trovato (Trapizzino) | IG: trovato (Trapizzino)</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
@@ -9996,32 +10162,32 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Margherì</t>
+          <t>Vanilla - Creams &amp; Fruits</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Via Sant'Ottavio, 51/C</t>
+          <t>Via Palazzo di Città, 7/B</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>011/0268025</t>
+          <t>011/4362745</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>www.margheripizza.it</t>
+          <t>www.vanillacreams.it</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>margheripizzaromana</t>
+          <t>VanillaCreamsAndFruits</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>margheripizza</t>
+          <t>vanillatorino</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -10051,7 +10217,7 @@
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (margheripizzaromana) | IG: trovato (margheripizza)</t>
+          <t>TF: non trovato | FB: trovato (VanillaCreamsAndFruits) | IG: trovato (vanillatorino)</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
@@ -10063,17 +10229,17 @@
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>Marilù fa il gelato</t>
+          <t>Lumeria</t>
         </is>
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>Via Nizza, 92</t>
+          <t>Via Reggio, 6/c</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t>011/7920082</t>
+          <t>011/19707614</t>
         </is>
       </c>
       <c r="D170" s="1" t="inlineStr"/>
@@ -10104,287 +10270,216 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Nivà</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Piazza Vittorio Veneto, 8</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>011/8125064</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>www.nivagelato.com</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>nivagelato</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>nivagelato</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>Snodo</t>
+        </is>
+      </c>
+      <c r="B171" s="1" t="inlineStr">
+        <is>
+          <t>Corso Castefidardo, 22</t>
+        </is>
+      </c>
+      <c r="C171" s="1" t="inlineStr">
+        <is>
+          <t>011/0243771</t>
+        </is>
+      </c>
+      <c r="D171" s="1" t="inlineStr"/>
+      <c r="E171" s="1" t="inlineStr"/>
+      <c r="F171" s="1" t="inlineStr"/>
+      <c r="G171" s="1" t="inlineStr"/>
+      <c r="H171" s="1" t="inlineStr"/>
+      <c r="I171" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J171" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O171" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q171" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (nivagelato) | IG: trovato (nivagelato)</t>
-        </is>
-      </c>
-      <c r="R171" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
+      <c r="K171" s="1" t="inlineStr"/>
+      <c r="L171" s="1" t="inlineStr"/>
+      <c r="M171" s="1" t="inlineStr"/>
+      <c r="N171" s="1" t="inlineStr"/>
+      <c r="O171" s="1" t="inlineStr"/>
+      <c r="P171" s="1" t="inlineStr"/>
+      <c r="Q171" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R171" s="1" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Papalele</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Corso Guglielmo Marconi, 23/A</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>011/9776990</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>www.papalele.it</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>papalele.gelatiepasticci</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>papalele.gelatiepasticci</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>Casa Clara</t>
+        </is>
+      </c>
+      <c r="B172" s="1" t="inlineStr">
+        <is>
+          <t>Via Stradella, 187/D</t>
+        </is>
+      </c>
+      <c r="C172" s="1" t="inlineStr">
+        <is>
+          <t>351/7516005</t>
+        </is>
+      </c>
+      <c r="D172" s="1" t="inlineStr"/>
+      <c r="E172" s="1" t="inlineStr"/>
+      <c r="F172" s="1" t="inlineStr"/>
+      <c r="G172" s="1" t="inlineStr"/>
+      <c r="H172" s="1" t="inlineStr"/>
+      <c r="I172" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J172" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O172" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q172" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (papalele.gelatiepasticci) | IG: trovato (papalele.gelatiepasticci)</t>
-        </is>
-      </c>
-      <c r="R172" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
+      <c r="K172" s="1" t="inlineStr"/>
+      <c r="L172" s="1" t="inlineStr"/>
+      <c r="M172" s="1" t="inlineStr"/>
+      <c r="N172" s="1" t="inlineStr"/>
+      <c r="O172" s="1" t="inlineStr"/>
+      <c r="P172" s="1" t="inlineStr"/>
+      <c r="Q172" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R172" s="1" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Più di un gelato</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Via Cesare Battisti, 7/F</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>345/1862428</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>www.piudiungelato.it</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Piudiungelato</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>piudiungelato</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>Ciacci</t>
+        </is>
+      </c>
+      <c r="B173" s="1" t="inlineStr">
+        <is>
+          <t>Corso Belgio, 176</t>
+        </is>
+      </c>
+      <c r="C173" s="1" t="inlineStr">
+        <is>
+          <t>392/0073855</t>
+        </is>
+      </c>
+      <c r="D173" s="1" t="inlineStr"/>
+      <c r="E173" s="1" t="inlineStr"/>
+      <c r="F173" s="1" t="inlineStr"/>
+      <c r="G173" s="1" t="inlineStr"/>
+      <c r="H173" s="1" t="inlineStr"/>
+      <c r="I173" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J173" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O173" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q173" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (Piudiungelato) | IG: trovato (piudiungelato)</t>
-        </is>
-      </c>
-      <c r="R173" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
+      <c r="K173" s="1" t="inlineStr"/>
+      <c r="L173" s="1" t="inlineStr"/>
+      <c r="M173" s="1" t="inlineStr"/>
+      <c r="N173" s="1" t="inlineStr"/>
+      <c r="O173" s="1" t="inlineStr"/>
+      <c r="P173" s="1" t="inlineStr"/>
+      <c r="Q173" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R173" s="1" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Roberta - focacceria genovese</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Via San Tommaso, 8</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>333/5826556</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>focacceriaroberta</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>robertafocacceria</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>Dolce Mania dei Fratelli Lepori</t>
+        </is>
+      </c>
+      <c r="B174" s="1" t="inlineStr">
+        <is>
+          <t>Via Guido Reni, 205</t>
+        </is>
+      </c>
+      <c r="C174" s="1" t="inlineStr">
+        <is>
+          <t>329/6543797</t>
+        </is>
+      </c>
+      <c r="D174" s="1" t="inlineStr"/>
+      <c r="E174" s="1" t="inlineStr"/>
+      <c r="F174" s="1" t="inlineStr"/>
+      <c r="G174" s="1" t="inlineStr"/>
+      <c r="H174" s="1" t="inlineStr"/>
+      <c r="I174" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J174" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O174" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q174" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (focacceriaroberta) | IG: trovato (robertafocacceria)</t>
-        </is>
-      </c>
-      <c r="R174" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
+      <c r="K174" s="1" t="inlineStr"/>
+      <c r="L174" s="1" t="inlineStr"/>
+      <c r="M174" s="1" t="inlineStr"/>
+      <c r="N174" s="1" t="inlineStr"/>
+      <c r="O174" s="1" t="inlineStr"/>
+      <c r="P174" s="1" t="inlineStr"/>
+      <c r="Q174" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R174" s="1" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>Siculo</t>
+          <t>Gelateria La Tosca</t>
         </is>
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>Via S. Quintino, 31</t>
+          <t>Via Luigi Cibrario, 50</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
         <is>
-          <t>011/542529 - 011/18838357</t>
+          <t>011/4379807</t>
         </is>
       </c>
       <c r="D175" s="1" t="inlineStr"/>
@@ -10415,342 +10510,247 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Silvano Gelato d'Altri Tempi</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Via Nizza, 142</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>011/6677262</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>www.gelateriasilvano.it</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Silvanogelatodaltritempi</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>silvanogelatodaltritempi</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>Gelati D'Antan</t>
+        </is>
+      </c>
+      <c r="B176" s="1" t="inlineStr">
+        <is>
+          <t>Via Nicola Fabrizi, 37/C</t>
+        </is>
+      </c>
+      <c r="C176" s="1" t="inlineStr">
+        <is>
+          <t>331/4675801</t>
+        </is>
+      </c>
+      <c r="D176" s="1" t="inlineStr"/>
+      <c r="E176" s="1" t="inlineStr"/>
+      <c r="F176" s="1" t="inlineStr"/>
+      <c r="G176" s="1" t="inlineStr"/>
+      <c r="H176" s="1" t="inlineStr"/>
+      <c r="I176" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J176" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O176" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q176" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (Silvanogelatodaltritempi) | IG: trovato (silvanogelatodaltritempi)</t>
-        </is>
-      </c>
-      <c r="R176" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
+      <c r="K176" s="1" t="inlineStr"/>
+      <c r="L176" s="1" t="inlineStr"/>
+      <c r="M176" s="1" t="inlineStr"/>
+      <c r="N176" s="1" t="inlineStr"/>
+      <c r="O176" s="1" t="inlineStr"/>
+      <c r="P176" s="1" t="inlineStr"/>
+      <c r="Q176" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R176" s="1" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Taglio - La pizza per fetta</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Largo IV Marzo, 17/C</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>011/5215575</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>www.taglioperfetta.com</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>taglioperfetta</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>taglioperfetta</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>Gelato DOK Dell'Agnese</t>
+        </is>
+      </c>
+      <c r="B177" s="1" t="inlineStr">
+        <is>
+          <t>Corso Unione Sovietica, 415</t>
+        </is>
+      </c>
+      <c r="C177" s="1" t="inlineStr">
+        <is>
+          <t>011/616157</t>
+        </is>
+      </c>
+      <c r="D177" s="1" t="inlineStr"/>
+      <c r="E177" s="1" t="inlineStr"/>
+      <c r="F177" s="1" t="inlineStr"/>
+      <c r="G177" s="1" t="inlineStr"/>
+      <c r="H177" s="1" t="inlineStr"/>
+      <c r="I177" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J177" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O177" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q177" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (taglioperfetta) | IG: trovato (taglioperfetta)</t>
-        </is>
-      </c>
-      <c r="R177" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
+      <c r="K177" s="1" t="inlineStr"/>
+      <c r="L177" s="1" t="inlineStr"/>
+      <c r="M177" s="1" t="inlineStr"/>
+      <c r="N177" s="1" t="inlineStr"/>
+      <c r="O177" s="1" t="inlineStr"/>
+      <c r="P177" s="1" t="inlineStr"/>
+      <c r="Q177" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R177" s="1" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Tellia</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Via Maria Vittoria, 20</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>011/2481776</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>www.tellia.it</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>TelliaTorino</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>telliatorino</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>Il Gelato Amico</t>
+        </is>
+      </c>
+      <c r="B178" s="1" t="inlineStr">
+        <is>
+          <t>Via Principi d'Acaja, 47</t>
+        </is>
+      </c>
+      <c r="C178" s="1" t="inlineStr">
+        <is>
+          <t>347/3492737</t>
+        </is>
+      </c>
+      <c r="D178" s="1" t="inlineStr"/>
+      <c r="E178" s="1" t="inlineStr"/>
+      <c r="F178" s="1" t="inlineStr"/>
+      <c r="G178" s="1" t="inlineStr"/>
+      <c r="H178" s="1" t="inlineStr"/>
+      <c r="I178" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J178" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O178" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q178" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (TelliaTorino) | IG: trovato (telliatorino)</t>
-        </is>
-      </c>
-      <c r="R178" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
+      <c r="K178" s="1" t="inlineStr"/>
+      <c r="L178" s="1" t="inlineStr"/>
+      <c r="M178" s="1" t="inlineStr"/>
+      <c r="N178" s="1" t="inlineStr"/>
+      <c r="O178" s="1" t="inlineStr"/>
+      <c r="P178" s="1" t="inlineStr"/>
+      <c r="Q178" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R178" s="1" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Trapizzino</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Piazza Carlo Emanuele II, 17</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>011/18755933</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>www.trapizzino.it</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Trapizzino</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>Trapizzino</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>Marilù fa il gelato</t>
+        </is>
+      </c>
+      <c r="B179" s="1" t="inlineStr">
+        <is>
+          <t>Via Nizza, 92</t>
+        </is>
+      </c>
+      <c r="C179" s="1" t="inlineStr">
+        <is>
+          <t>011/7920082</t>
+        </is>
+      </c>
+      <c r="D179" s="1" t="inlineStr"/>
+      <c r="E179" s="1" t="inlineStr"/>
+      <c r="F179" s="1" t="inlineStr"/>
+      <c r="G179" s="1" t="inlineStr"/>
+      <c r="H179" s="1" t="inlineStr"/>
+      <c r="I179" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J179" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O179" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q179" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (Trapizzino) | IG: trovato (Trapizzino)</t>
-        </is>
-      </c>
-      <c r="R179" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
+      <c r="K179" s="1" t="inlineStr"/>
+      <c r="L179" s="1" t="inlineStr"/>
+      <c r="M179" s="1" t="inlineStr"/>
+      <c r="N179" s="1" t="inlineStr"/>
+      <c r="O179" s="1" t="inlineStr"/>
+      <c r="P179" s="1" t="inlineStr"/>
+      <c r="Q179" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R179" s="1" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Vanilla - Creams &amp; Fruits</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Via Palazzo di Città, 7/B</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>011/4362745</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>www.vanillacreams.it</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>VanillaCreamsAndFruits</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>vanillatorino</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>Siculo</t>
+        </is>
+      </c>
+      <c r="B180" s="1" t="inlineStr">
+        <is>
+          <t>Via S. Quintino, 31</t>
+        </is>
+      </c>
+      <c r="C180" s="1" t="inlineStr">
+        <is>
+          <t>011/542529 - 011/18838357</t>
+        </is>
+      </c>
+      <c r="D180" s="1" t="inlineStr"/>
+      <c r="E180" s="1" t="inlineStr"/>
+      <c r="F180" s="1" t="inlineStr"/>
+      <c r="G180" s="1" t="inlineStr"/>
+      <c r="H180" s="1" t="inlineStr"/>
+      <c r="I180" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J180" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O180" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q180" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (VanillaCreamsAndFruits) | IG: trovato (vanillatorino)</t>
-        </is>
-      </c>
-      <c r="R180" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
+      <c r="K180" s="1" t="inlineStr"/>
+      <c r="L180" s="1" t="inlineStr"/>
+      <c r="M180" s="1" t="inlineStr"/>
+      <c r="N180" s="1" t="inlineStr"/>
+      <c r="O180" s="1" t="inlineStr"/>
+      <c r="P180" s="1" t="inlineStr"/>
+      <c r="Q180" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R180" s="1" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Torino_2027.xlsx
+++ b/Verifica_Torino_2027.xlsx
@@ -10270,7 +10270,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="R171" s="1" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -10414,7 +10414,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -10606,7 +10606,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Torino_2027.xlsx
+++ b/Verifica_Torino_2027.xlsx
@@ -10270,7 +10270,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="R171" s="1" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -10414,7 +10414,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -10606,7 +10606,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Torino_2027.xlsx
+++ b/Verifica_Torino_2027.xlsx
@@ -10270,7 +10270,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="R171" s="1" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -10414,7 +10414,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -10606,7 +10606,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Torino_2027.xlsx
+++ b/Verifica_Torino_2027.xlsx
@@ -10270,7 +10270,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="R171" s="1" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -10414,7 +10414,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -10606,7 +10606,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Torino_2027.xlsx
+++ b/Verifica_Torino_2027.xlsx
@@ -10270,7 +10270,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="R171" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -10414,7 +10414,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -10606,7 +10606,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Torino_2027.xlsx
+++ b/Verifica_Torino_2027.xlsx
@@ -10270,7 +10270,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="R171" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -10414,7 +10414,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -10606,7 +10606,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Torino_2027.xlsx
+++ b/Verifica_Torino_2027.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
-        <bgColor rgb="00FFFF00"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -10227,530 +10220,459 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="inlineStr">
+      <c r="A170" t="inlineStr">
         <is>
           <t>Lumeria</t>
         </is>
       </c>
-      <c r="B170" s="1" t="inlineStr">
+      <c r="B170" t="inlineStr">
         <is>
           <t>Via Reggio, 6/c</t>
         </is>
       </c>
-      <c r="C170" s="1" t="inlineStr">
+      <c r="C170" t="inlineStr">
         <is>
           <t>011/19707614</t>
         </is>
       </c>
-      <c r="D170" s="1" t="inlineStr"/>
-      <c r="E170" s="1" t="inlineStr"/>
-      <c r="F170" s="1" t="inlineStr"/>
-      <c r="G170" s="1" t="inlineStr"/>
-      <c r="H170" s="1" t="inlineStr"/>
-      <c r="I170" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J170" s="1" t="inlineStr">
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K170" s="1" t="inlineStr"/>
-      <c r="L170" s="1" t="inlineStr"/>
-      <c r="M170" s="1" t="inlineStr"/>
-      <c r="N170" s="1" t="inlineStr"/>
-      <c r="O170" s="1" t="inlineStr"/>
-      <c r="P170" s="1" t="inlineStr"/>
-      <c r="Q170" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R170" s="1" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '17', 'closes': '02'}, 'venerdì': {'opens': '17', 'closes'</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="inlineStr">
+      <c r="A171" t="inlineStr">
         <is>
           <t>Snodo</t>
         </is>
       </c>
-      <c r="B171" s="1" t="inlineStr">
+      <c r="B171" t="inlineStr">
         <is>
           <t>Corso Castefidardo, 22</t>
         </is>
       </c>
-      <c r="C171" s="1" t="inlineStr">
+      <c r="C171" t="inlineStr">
         <is>
           <t>011/0243771</t>
         </is>
       </c>
-      <c r="D171" s="1" t="inlineStr"/>
-      <c r="E171" s="1" t="inlineStr"/>
-      <c r="F171" s="1" t="inlineStr"/>
-      <c r="G171" s="1" t="inlineStr"/>
-      <c r="H171" s="1" t="inlineStr"/>
-      <c r="I171" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J171" s="1" t="inlineStr">
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K171" s="1" t="inlineStr"/>
-      <c r="L171" s="1" t="inlineStr"/>
-      <c r="M171" s="1" t="inlineStr"/>
-      <c r="N171" s="1" t="inlineStr"/>
-      <c r="O171" s="1" t="inlineStr"/>
-      <c r="P171" s="1" t="inlineStr"/>
-      <c r="Q171" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R171" s="1" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '08', 'closes': '01'}, 'venerdì': {'opens': '08', 'closes'</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.0 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="inlineStr">
+      <c r="A172" t="inlineStr">
         <is>
           <t>Casa Clara</t>
         </is>
       </c>
-      <c r="B172" s="1" t="inlineStr">
+      <c r="B172" t="inlineStr">
         <is>
           <t>Via Stradella, 187/D</t>
         </is>
       </c>
-      <c r="C172" s="1" t="inlineStr">
+      <c r="C172" t="inlineStr">
         <is>
           <t>351/7516005</t>
         </is>
       </c>
-      <c r="D172" s="1" t="inlineStr"/>
-      <c r="E172" s="1" t="inlineStr"/>
-      <c r="F172" s="1" t="inlineStr"/>
-      <c r="G172" s="1" t="inlineStr"/>
-      <c r="H172" s="1" t="inlineStr"/>
-      <c r="I172" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J172" s="1" t="inlineStr">
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K172" s="1" t="inlineStr"/>
-      <c r="L172" s="1" t="inlineStr"/>
-      <c r="M172" s="1" t="inlineStr"/>
-      <c r="N172" s="1" t="inlineStr"/>
-      <c r="O172" s="1" t="inlineStr"/>
-      <c r="P172" s="1" t="inlineStr"/>
-      <c r="Q172" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R172" s="1" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '15', 'closes': '00'}, 'venerdì': {'opens': '15', 'closes'</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.1 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="inlineStr">
+      <c r="A173" t="inlineStr">
         <is>
           <t>Ciacci</t>
         </is>
       </c>
-      <c r="B173" s="1" t="inlineStr">
+      <c r="B173" t="inlineStr">
         <is>
           <t>Corso Belgio, 176</t>
         </is>
       </c>
-      <c r="C173" s="1" t="inlineStr">
+      <c r="C173" t="inlineStr">
         <is>
           <t>392/0073855</t>
         </is>
       </c>
-      <c r="D173" s="1" t="inlineStr"/>
-      <c r="E173" s="1" t="inlineStr"/>
-      <c r="F173" s="1" t="inlineStr"/>
-      <c r="G173" s="1" t="inlineStr"/>
-      <c r="H173" s="1" t="inlineStr"/>
-      <c r="I173" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J173" s="1" t="inlineStr">
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K173" s="1" t="inlineStr"/>
-      <c r="L173" s="1" t="inlineStr"/>
-      <c r="M173" s="1" t="inlineStr"/>
-      <c r="N173" s="1" t="inlineStr"/>
-      <c r="O173" s="1" t="inlineStr"/>
-      <c r="P173" s="1" t="inlineStr"/>
-      <c r="Q173" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R173" s="1" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '11:30', 'closes': '23'}, 'venerdì': {'opens': '11:30', 'c</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="inlineStr">
+      <c r="A174" t="inlineStr">
         <is>
           <t>Dolce Mania dei Fratelli Lepori</t>
         </is>
       </c>
-      <c r="B174" s="1" t="inlineStr">
+      <c r="B174" t="inlineStr">
         <is>
           <t>Via Guido Reni, 205</t>
         </is>
       </c>
-      <c r="C174" s="1" t="inlineStr">
+      <c r="C174" t="inlineStr">
         <is>
           <t>329/6543797</t>
         </is>
       </c>
-      <c r="D174" s="1" t="inlineStr"/>
-      <c r="E174" s="1" t="inlineStr"/>
-      <c r="F174" s="1" t="inlineStr"/>
-      <c r="G174" s="1" t="inlineStr"/>
-      <c r="H174" s="1" t="inlineStr"/>
-      <c r="I174" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J174" s="1" t="inlineStr">
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K174" s="1" t="inlineStr"/>
-      <c r="L174" s="1" t="inlineStr"/>
-      <c r="M174" s="1" t="inlineStr"/>
-      <c r="N174" s="1" t="inlineStr"/>
-      <c r="O174" s="1" t="inlineStr"/>
-      <c r="P174" s="1" t="inlineStr"/>
-      <c r="Q174" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R174" s="1" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '14', 'closes': '00'}, 'venerdì': {'opens': '14', 'closes'</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="inlineStr">
+      <c r="A175" t="inlineStr">
         <is>
           <t>Gelateria La Tosca</t>
         </is>
       </c>
-      <c r="B175" s="1" t="inlineStr">
+      <c r="B175" t="inlineStr">
         <is>
           <t>Via Luigi Cibrario, 50</t>
         </is>
       </c>
-      <c r="C175" s="1" t="inlineStr">
+      <c r="C175" t="inlineStr">
         <is>
           <t>011/4379807</t>
         </is>
       </c>
-      <c r="D175" s="1" t="inlineStr"/>
-      <c r="E175" s="1" t="inlineStr"/>
-      <c r="F175" s="1" t="inlineStr"/>
-      <c r="G175" s="1" t="inlineStr"/>
-      <c r="H175" s="1" t="inlineStr"/>
-      <c r="I175" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J175" s="1" t="inlineStr">
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K175" s="1" t="inlineStr"/>
-      <c r="L175" s="1" t="inlineStr"/>
-      <c r="M175" s="1" t="inlineStr"/>
-      <c r="N175" s="1" t="inlineStr"/>
-      <c r="O175" s="1" t="inlineStr"/>
-      <c r="P175" s="1" t="inlineStr"/>
-      <c r="Q175" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R175" s="1" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '08:30', 'closes': '22'}, 'venerdì': {'opens': '08:30', 'c</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="inlineStr">
+      <c r="A176" t="inlineStr">
         <is>
           <t>Gelati D'Antan</t>
         </is>
       </c>
-      <c r="B176" s="1" t="inlineStr">
+      <c r="B176" t="inlineStr">
         <is>
           <t>Via Nicola Fabrizi, 37/C</t>
         </is>
       </c>
-      <c r="C176" s="1" t="inlineStr">
+      <c r="C176" t="inlineStr">
         <is>
           <t>331/4675801</t>
         </is>
       </c>
-      <c r="D176" s="1" t="inlineStr"/>
-      <c r="E176" s="1" t="inlineStr"/>
-      <c r="F176" s="1" t="inlineStr"/>
-      <c r="G176" s="1" t="inlineStr"/>
-      <c r="H176" s="1" t="inlineStr"/>
-      <c r="I176" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J176" s="1" t="inlineStr">
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K176" s="1" t="inlineStr"/>
-      <c r="L176" s="1" t="inlineStr"/>
-      <c r="M176" s="1" t="inlineStr"/>
-      <c r="N176" s="1" t="inlineStr"/>
-      <c r="O176" s="1" t="inlineStr"/>
-      <c r="P176" s="1" t="inlineStr"/>
-      <c r="Q176" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R176" s="1" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '11:30', 'closes': '23'}, 'venerdì': {'opens': '11:30', 'c</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="inlineStr">
+      <c r="A177" t="inlineStr">
         <is>
           <t>Gelato DOK Dell'Agnese</t>
         </is>
       </c>
-      <c r="B177" s="1" t="inlineStr">
+      <c r="B177" t="inlineStr">
         <is>
           <t>Corso Unione Sovietica, 415</t>
         </is>
       </c>
-      <c r="C177" s="1" t="inlineStr">
+      <c r="C177" t="inlineStr">
         <is>
           <t>011/616157</t>
         </is>
       </c>
-      <c r="D177" s="1" t="inlineStr"/>
-      <c r="E177" s="1" t="inlineStr"/>
-      <c r="F177" s="1" t="inlineStr"/>
-      <c r="G177" s="1" t="inlineStr"/>
-      <c r="H177" s="1" t="inlineStr"/>
-      <c r="I177" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J177" s="1" t="inlineStr">
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K177" s="1" t="inlineStr"/>
-      <c r="L177" s="1" t="inlineStr"/>
-      <c r="M177" s="1" t="inlineStr"/>
-      <c r="N177" s="1" t="inlineStr"/>
-      <c r="O177" s="1" t="inlineStr"/>
-      <c r="P177" s="1" t="inlineStr"/>
-      <c r="Q177" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R177" s="1" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '08, 15', 'closes': '13, 19:30', 'break': '13–15'}, 'vener</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="inlineStr">
+      <c r="A178" t="inlineStr">
         <is>
           <t>Il Gelato Amico</t>
         </is>
       </c>
-      <c r="B178" s="1" t="inlineStr">
+      <c r="B178" t="inlineStr">
         <is>
           <t>Via Principi d'Acaja, 47</t>
         </is>
       </c>
-      <c r="C178" s="1" t="inlineStr">
+      <c r="C178" t="inlineStr">
         <is>
           <t>347/3492737</t>
         </is>
       </c>
-      <c r="D178" s="1" t="inlineStr"/>
-      <c r="E178" s="1" t="inlineStr"/>
-      <c r="F178" s="1" t="inlineStr"/>
-      <c r="G178" s="1" t="inlineStr"/>
-      <c r="H178" s="1" t="inlineStr"/>
-      <c r="I178" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J178" s="1" t="inlineStr">
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K178" s="1" t="inlineStr"/>
-      <c r="L178" s="1" t="inlineStr"/>
-      <c r="M178" s="1" t="inlineStr"/>
-      <c r="N178" s="1" t="inlineStr"/>
-      <c r="O178" s="1" t="inlineStr"/>
-      <c r="P178" s="1" t="inlineStr"/>
-      <c r="Q178" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R178" s="1" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="inlineStr">
+      <c r="A179" t="inlineStr">
         <is>
           <t>Marilù fa il gelato</t>
         </is>
       </c>
-      <c r="B179" s="1" t="inlineStr">
+      <c r="B179" t="inlineStr">
         <is>
           <t>Via Nizza, 92</t>
         </is>
       </c>
-      <c r="C179" s="1" t="inlineStr">
+      <c r="C179" t="inlineStr">
         <is>
           <t>011/7920082</t>
         </is>
       </c>
-      <c r="D179" s="1" t="inlineStr"/>
-      <c r="E179" s="1" t="inlineStr"/>
-      <c r="F179" s="1" t="inlineStr"/>
-      <c r="G179" s="1" t="inlineStr"/>
-      <c r="H179" s="1" t="inlineStr"/>
-      <c r="I179" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J179" s="1" t="inlineStr">
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K179" s="1" t="inlineStr"/>
-      <c r="L179" s="1" t="inlineStr"/>
-      <c r="M179" s="1" t="inlineStr"/>
-      <c r="N179" s="1" t="inlineStr"/>
-      <c r="O179" s="1" t="inlineStr"/>
-      <c r="P179" s="1" t="inlineStr"/>
-      <c r="Q179" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R179" s="1" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12', 'closes': '22'}, 'venerdì': {'opens': '12', 'closes'</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="inlineStr">
+      <c r="A180" t="inlineStr">
         <is>
           <t>Siculo</t>
         </is>
       </c>
-      <c r="B180" s="1" t="inlineStr">
+      <c r="B180" t="inlineStr">
         <is>
           <t>Via S. Quintino, 31</t>
         </is>
       </c>
-      <c r="C180" s="1" t="inlineStr">
+      <c r="C180" t="inlineStr">
         <is>
           <t>011/542529 - 011/18838357</t>
         </is>
       </c>
-      <c r="D180" s="1" t="inlineStr"/>
-      <c r="E180" s="1" t="inlineStr"/>
-      <c r="F180" s="1" t="inlineStr"/>
-      <c r="G180" s="1" t="inlineStr"/>
-      <c r="H180" s="1" t="inlineStr"/>
-      <c r="I180" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J180" s="1" t="inlineStr">
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K180" s="1" t="inlineStr"/>
-      <c r="L180" s="1" t="inlineStr"/>
-      <c r="M180" s="1" t="inlineStr"/>
-      <c r="N180" s="1" t="inlineStr"/>
-      <c r="O180" s="1" t="inlineStr"/>
-      <c r="P180" s="1" t="inlineStr"/>
-      <c r="Q180" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R180" s="1" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12', 'closes': '00'}, 'venerdì': {'opens': '12', 'closes'</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
